--- a/data/trans_orig/P37A$vacunaempresa-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunaempresa-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1018948</t>
+          <t>1018834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1029684</t>
+          <t>1029553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1306722</t>
+          <t>1307584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2331397</t>
+          <t>2331351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2342274</t>
+          <t>2342920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>35913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1667758</t>
+          <t>1666924</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1685027</t>
+          <t>1684246</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1572267</t>
+          <t>1572300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1583751</t>
+          <t>1583712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3245793</t>
+          <t>3245173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3265851</t>
+          <t>3265860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31681</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529833</t>
+          <t>529318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543974</t>
+          <t>543948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463101</t>
+          <t>463280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473391</t>
+          <t>473516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>996139</t>
+          <t>997161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015121</t>
+          <t>1015264</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48014</t>
+          <t>48567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>39214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66045</t>
+          <t>68139</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3228529</t>
+          <t>3227976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3252273</t>
+          <t>3251959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3350808</t>
+          <t>3351025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3367600</t>
+          <t>3368201</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6589696</t>
+          <t>6587602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6616458</t>
+          <t>6616527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>968113</t>
+          <t>968111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2305067</t>
+          <t>2306756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40977</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29258</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32206</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>60519</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1922980</t>
+          <t>1923771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1945941</t>
+          <t>1947272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1728545</t>
+          <t>1728694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1746197</t>
+          <t>1746709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3660953</t>
+          <t>3661241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3689554</t>
+          <t>3690406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>28833</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44253</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452204</t>
+          <t>452348</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471217</t>
+          <t>470395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435082</t>
+          <t>435552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>452673</t>
+          <t>452579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>895560</t>
+          <t>893322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>919647</t>
+          <t>919245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33950</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>63554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21340</t>
+          <t>21177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44994</t>
+          <t>47275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60235</t>
+          <t>59470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98268</t>
+          <t>98105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3355389</t>
+          <t>3356228</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3385832</t>
+          <t>3386907</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3509236</t>
+          <t>3506955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3532890</t>
+          <t>3533053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6875744</t>
+          <t>6875907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6913777</t>
+          <t>6914542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>748039</t>
+          <t>749077</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1743776</t>
+          <t>1743536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2059403</t>
+          <t>2059025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2072420</t>
+          <t>2072488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1970946</t>
+          <t>1970618</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1984155</t>
+          <t>1983597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4035752</t>
+          <t>4035861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4053602</t>
+          <t>4053529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25050</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535469</t>
+          <t>535229</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545695</t>
+          <t>545844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530406</t>
+          <t>531682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544384</t>
+          <t>544586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1070977</t>
+          <t>1071317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1088001</t>
+          <t>1087895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25458</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>23946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48243</t>
+          <t>49313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3352160</t>
+          <t>3352614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3369601</t>
+          <t>3369430</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3502653</t>
+          <t>3503044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3521038</t>
+          <t>3520581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6861475</t>
+          <t>6860405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6886316</t>
+          <t>6885772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5650,27 +5650,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>512609</t>
+          <t>576221</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>507108</t>
+          <t>569320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>752188</t>
+          <t>818292</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>747287</t>
+          <t>813244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>754371</t>
+          <t>820694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1264798</t>
+          <t>1394513</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1257658</t>
+          <t>1387404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1268199</t>
+          <t>1397962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,102 +5880,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52008</t>
+          <t>54517</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34040</t>
+          <t>40875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70653</t>
+          <t>70590</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>66009</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>52469</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>81159</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>120526</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>99788</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>141184</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>62952</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>45512</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>79822</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>114960</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>90039</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>141311</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -5993,102 +5993,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2238319</t>
+          <t>2176049</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2219674</t>
+          <t>2159976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2256287</t>
+          <t>2189691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2105383</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2090233</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2118923</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4775</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4281433</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4260775</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4302171</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>97,73%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2174871</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2158001</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2192311</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,19%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4413190</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4386839</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4438111</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35746</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25197</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50029</t>
+          <t>51246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33075</t>
+          <t>37284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>80402</t>
+          <t>85629</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63647</t>
+          <t>68787</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99250</t>
+          <t>102620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>610877</t>
+          <t>673605</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596594</t>
+          <t>660341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621426</t>
+          <t>684046</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>615806</t>
+          <t>687230</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>603730</t>
+          <t>671850</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>627388</t>
+          <t>697593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1226684</t>
+          <t>1360835</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1207836</t>
+          <t>1343844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1243439</t>
+          <t>1377677</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67664</t>
+          <t>76225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111326</t>
+          <t>116610</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89273</t>
+          <t>98433</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133384</t>
+          <t>137782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>201011</t>
+          <t>212209</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170364</t>
+          <t>186413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>234777</t>
+          <t>241161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3361807</t>
+          <t>3425876</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3340563</t>
+          <t>3404073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3384225</t>
+          <t>3444458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3542865</t>
+          <t>3610905</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3520410</t>
+          <t>3590525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3564521</t>
+          <t>3629874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6904672</t>
+          <t>7036781</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6870906</t>
+          <t>7007829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6935319</t>
+          <t>7062577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
